--- a/deliverables/crown-menu.xlsx
+++ b/deliverables/crown-menu.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="151">
   <si>
     <t>Category</t>
   </si>
@@ -434,6 +434,36 @@
   </si>
   <si>
     <t>ستێکی مریشک</t>
+  </si>
+  <si>
+    <t>Hookah</t>
+  </si>
+  <si>
+    <t>Nargila Crown</t>
+  </si>
+  <si>
+    <t>نركيلة كراون</t>
+  </si>
+  <si>
+    <t>ناڕگیلەی کراون</t>
+  </si>
+  <si>
+    <t>Nargila Normal</t>
+  </si>
+  <si>
+    <t>نركيلة عادي</t>
+  </si>
+  <si>
+    <t>ناڕگیلەی ئاسایی</t>
+  </si>
+  <si>
+    <t>Nargila VIP</t>
+  </si>
+  <si>
+    <t>نركيلة VIP</t>
+  </si>
+  <si>
+    <t>ناڕگیلەی VIP</t>
   </si>
 </sst>
 </file>
@@ -814,7 +844,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3755,6 +3785,93 @@
         <v>11</v>
       </c>
     </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>141</v>
+      </c>
+      <c r="B102" t="s">
+        <v>142</v>
+      </c>
+      <c r="C102" t="s">
+        <v>143</v>
+      </c>
+      <c r="D102" t="s">
+        <v>144</v>
+      </c>
+      <c r="E102" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102">
+        <v>50000</v>
+      </c>
+      <c r="G102" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>141</v>
+      </c>
+      <c r="B103" t="s">
+        <v>145</v>
+      </c>
+      <c r="C103" t="s">
+        <v>146</v>
+      </c>
+      <c r="D103" t="s">
+        <v>147</v>
+      </c>
+      <c r="E103" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103">
+        <v>20000</v>
+      </c>
+      <c r="G103" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>141</v>
+      </c>
+      <c r="B104" t="s">
+        <v>148</v>
+      </c>
+      <c r="C104" t="s">
+        <v>149</v>
+      </c>
+      <c r="D104" t="s">
+        <v>150</v>
+      </c>
+      <c r="E104" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104">
+        <v>30000</v>
+      </c>
+      <c r="G104" t="s">
+        <v>11</v>
+      </c>
+      <c r="H104" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
